--- a/table/tabelleDivList_protocolCore.xlsx
+++ b/table/tabelleDivList_protocolCore.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBDAC08-27F6-476D-B706-617CFA6FDB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425962EF-3CE2-4B85-BC4B-CFDFB5B61C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle diverse" sheetId="1" r:id="rId1"/>
+    <sheet name="Colonne alfanumeriche" sheetId="2" r:id="rId2"/>
+    <sheet name="Colonne numeriche" sheetId="3" r:id="rId3"/>
+    <sheet name="Lista Valori (dati)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,9 +27,167 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+  <si>
+    <t>N° tabella</t>
+  </si>
+  <si>
+    <t>Descrizione</t>
+  </si>
+  <si>
+    <t>Descr. breve</t>
+  </si>
+  <si>
+    <t>Modulo</t>
+  </si>
+  <si>
+    <t>Cod.Att</t>
+  </si>
+  <si>
+    <t>Cod.accesso</t>
+  </si>
+  <si>
+    <t>Modificabile</t>
+  </si>
+  <si>
+    <t>Filtro Società</t>
+  </si>
+  <si>
+    <t>Filtro Legislazione</t>
+  </si>
+  <si>
+    <t>Legisl. Obblig</t>
+  </si>
+  <si>
+    <t>Flag attivo</t>
+  </si>
+  <si>
+    <t>Lungh. Modificabile</t>
+  </si>
+  <si>
+    <t>Lungh</t>
+  </si>
+  <si>
+    <t>Tab dipendenza</t>
+  </si>
+  <si>
+    <t>Controller ArgoX3 API (AX3M)</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Supervisore</t>
+  </si>
+  <si>
+    <t>YAX3M</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>N° Tabella</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Codice</t>
+  </si>
+  <si>
+    <t>Nome Colonna alfanumerica 1</t>
+  </si>
+  <si>
+    <t>Nome Colonna numerica 1</t>
+  </si>
+  <si>
+    <t>CreazioneCliente</t>
+  </si>
+  <si>
+    <t>CalcoloGiacenza</t>
+  </si>
+  <si>
+    <t>CambioStock</t>
+  </si>
+  <si>
+    <t>Uscita</t>
+  </si>
+  <si>
+    <t>Entrata</t>
+  </si>
+  <si>
+    <t>RicercaCliente</t>
+  </si>
+  <si>
+    <t>OrdineDiVendita</t>
+  </si>
+  <si>
+    <t>RicercaOrdineDiVendita</t>
+  </si>
+  <si>
+    <t>valori (col alfanum1)</t>
+  </si>
+  <si>
+    <t>valori (col num1)</t>
+  </si>
+  <si>
+    <t>Nome Colonna alfanumerica2</t>
+  </si>
+  <si>
+    <t>valori (col alfanum2)</t>
+  </si>
+  <si>
+    <t>Nome Colonna numerica 2</t>
+  </si>
+  <si>
+    <t>valori (col num2)</t>
+  </si>
+  <si>
+    <t>YAX3MBPC</t>
+  </si>
+  <si>
+    <t>YAX3MVCG</t>
+  </si>
+  <si>
+    <t>YYAX3MCSK</t>
+  </si>
+  <si>
+    <t>YAX3MSMO</t>
+  </si>
+  <si>
+    <t>YAX3MSMR</t>
+  </si>
+  <si>
+    <t>YAX3MSOH</t>
+  </si>
+  <si>
+    <t>YAX3MVBP</t>
+  </si>
+  <si>
+    <t>YAX3MVSO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -34,16 +195,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -51,12 +226,193 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -337,9 +693,418 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18">
+        <v>6002</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="19">
+        <v>10</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C9447B-9811-47AE-B1DA-7D9DAAA34DF7}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>6002</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B62E2546-A32B-4FE7-A1E0-889A6D1B74E6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>6002</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8487F6-795E-4097-8148-47201B3D5EC6}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>6002</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="9">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/table/tabelleDivList_protocolCore.xlsx
+++ b/table/tabelleDivList_protocolCore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425962EF-3CE2-4B85-BC4B-CFDFB5B61C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665EF40-0FDD-4285-9DE0-1740ACBE5A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle diverse" sheetId="1" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>Supervisore</t>
   </si>
   <si>
-    <t>YAX3M</t>
-  </si>
-  <si>
     <t>/</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>YAX3MVSO</t>
+  </si>
+  <si>
+    <t>YAX3C</t>
   </si>
 </sst>
 </file>
@@ -204,18 +204,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -400,7 +394,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -413,6 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -711,7 +705,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
@@ -756,63 +750,63 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>6002</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="19">
+      <c r="I3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="18">
         <v>10</v>
       </c>
-      <c r="N3" s="20" t="s">
-        <v>18</v>
+      <c r="N3" s="19" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -831,13 +825,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -868,13 +862,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -882,10 +876,10 @@
         <v>6002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -919,31 +913,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>42</v>
       </c>
       <c r="L1" s="15"/>
     </row>
@@ -956,16 +950,16 @@
         <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="6">
         <v>7</v>
@@ -975,16 +969,16 @@
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" s="7">
         <v>4</v>
@@ -994,16 +988,16 @@
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="7">
         <v>3</v>
@@ -1013,16 +1007,16 @@
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="7">
         <v>2</v>
@@ -1032,16 +1026,16 @@
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="7">
         <v>1</v>
@@ -1051,16 +1045,16 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="7">
         <v>5</v>
@@ -1070,16 +1064,16 @@
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="7">
         <v>8</v>
@@ -1089,16 +1083,16 @@
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="9">
         <v>6</v>

--- a/table/tabelleDivList_protocolCore.xlsx
+++ b/table/tabelleDivList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665EF40-0FDD-4285-9DE0-1740ACBE5A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AF7E11-023B-4329-96B5-5F36BB0BDC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle diverse" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="57">
   <si>
     <t>N° tabella</t>
   </si>
@@ -181,6 +181,24 @@
   </si>
   <si>
     <t>YAX3C</t>
+  </si>
+  <si>
+    <t>Controller ArgoX3 API (AX3M)(menùAlbero)</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>IdParent</t>
+  </si>
+  <si>
+    <t>IsNavButton</t>
+  </si>
+  <si>
+    <t>TreeLevel</t>
+  </si>
+  <si>
+    <t>GlobalOrder</t>
   </si>
 </sst>
 </file>
@@ -204,15 +222,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -313,6 +337,43 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -323,31 +384,27 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -382,9 +439,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -394,19 +448,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -687,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -704,109 +814,142 @@
     <col min="14" max="14" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:15" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17">
+      <c r="O1" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
         <v>6002</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="20">
         <v>10</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>6003</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="20">
+        <v>10</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -815,7 +958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C9447B-9811-47AE-B1DA-7D9DAAA34DF7}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -834,14 +977,38 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
         <v>6002</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>6003</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26">
+        <v>6003</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -852,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B62E2546-A32B-4FE7-A1E0-889A6D1B74E6}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -871,14 +1038,60 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
         <v>6002</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>6003</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="28">
+        <v>6003</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="28">
+        <v>6003</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26">
+        <v>6003</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
     </row>
@@ -889,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8487F6-795E-4097-8148-47201B3D5EC6}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -909,44 +1122,44 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="15"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29">
         <v>6002</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -966,8 +1179,8 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="4" t="s">
         <v>43</v>
       </c>
@@ -985,8 +1198,8 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="4" t="s">
         <v>44</v>
       </c>
@@ -1004,8 +1217,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
@@ -1023,8 +1236,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
@@ -1042,8 +1255,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="4" t="s">
         <v>47</v>
       </c>
@@ -1061,8 +1274,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1080,8 +1293,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="8" t="s">
         <v>49</v>
       </c>
@@ -1095,6 +1308,163 @@
         <v>24</v>
       </c>
       <c r="G10" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29">
+        <v>6003</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="33">
         <v>6</v>
       </c>
     </row>
